--- a/その他/ゲーム展示会/展示見積り.xlsx
+++ b/その他/ゲーム展示会/展示見積り.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y_araki\Documents\授業資料\Textbook\その他\ゲーム展示会\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC6F28E9-4C95-4D0D-B512-A7CEDDCB118B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9340C632-52AD-45D7-A047-AEADCBC22C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{014623EE-1EA6-4F77-A9E6-360ABCF67025}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{014623EE-1EA6-4F77-A9E6-360ABCF67025}"/>
   </bookViews>
   <sheets>
     <sheet name="展示" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t>総数</t>
     <rPh sb="0" eb="2">
@@ -99,6 +99,22 @@
     <t>目標</t>
     <rPh sb="0" eb="2">
       <t>モクヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>総数はお声を掛けられる企業数</t>
+    <rPh sb="0" eb="2">
+      <t>ソウスウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>コエ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>キギョウスウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -539,10 +555,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A785B56-DCB6-4F21-96E3-1CE9037169A1}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -551,7 +567,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -562,7 +578,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -573,13 +589,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="1"/>
+      <c r="B4" s="1">
+        <v>50</v>
+      </c>
       <c r="C4" s="1">
         <v>30</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
